--- a/data/trans_dic/P02E$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,62; 97,19</t>
+          <t>84,03; 97,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,85; 92,74</t>
+          <t>78,1; 92,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,02; 92,38</t>
+          <t>77,59; 93,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,76; 97,95</t>
+          <t>87,16; 97,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,42; 91,29</t>
+          <t>77,75; 91,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,69; 83,57</t>
+          <t>66,16; 83,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,08; 96,51</t>
+          <t>89,05; 96,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,72; 90,73</t>
+          <t>80,97; 90,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,35; 85,92</t>
+          <t>74,11; 85,96</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,09; 98,49</t>
+          <t>86,02; 98,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,68; 96,79</t>
+          <t>88,32; 96,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,41; 94,77</t>
+          <t>81,26; 94,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,06; 86,68</t>
+          <t>72,77; 86,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,01; 95,71</t>
+          <t>88,99; 96,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,46; 95,39</t>
+          <t>85,74; 95,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,77; 89,75</t>
+          <t>80,09; 89,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,82; 95,5</t>
+          <t>90,26; 95,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,67; 93,91</t>
+          <t>86,45; 94,26</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,3; 94,36</t>
+          <t>78,92; 94,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,32; 97,68</t>
+          <t>86,81; 97,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,84; 97,07</t>
+          <t>84,38; 96,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,64; 98,09</t>
+          <t>87,88; 98,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,53; 93,46</t>
+          <t>82,9; 94,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,44; 93,76</t>
+          <t>78,2; 93,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,25; 95,43</t>
+          <t>86,39; 95,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,95; 94,23</t>
+          <t>86,44; 94,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,65; 93,92</t>
+          <t>83,26; 93,62</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,86; 94,47</t>
+          <t>81,7; 94,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,45; 92,79</t>
+          <t>77,17; 93,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,32; 96,57</t>
+          <t>81,55; 96,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,47; 94,28</t>
+          <t>82,82; 94,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,45; 89,05</t>
+          <t>78,04; 89,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,87; 95,15</t>
+          <t>84,23; 95,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,69; 93,17</t>
+          <t>84,32; 93,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,35; 89,12</t>
+          <t>80,95; 89,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,39; 94,46</t>
+          <t>85,56; 94,08</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,13; 94,55</t>
+          <t>63,16; 94,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,24; 92,26</t>
+          <t>71,25; 92,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,93; 97,86</t>
+          <t>83,85; 98,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75,23; 95,71</t>
+          <t>76,54; 95,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,9; 93,54</t>
+          <t>80,23; 93,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,16; 96,68</t>
+          <t>83,45; 96,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,71; 92,65</t>
+          <t>76,07; 92,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,14; 91,35</t>
+          <t>79,7; 91,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,23; 96,2</t>
+          <t>87,46; 96,02</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,16; 96,52</t>
+          <t>78,18; 96,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,81; 97,78</t>
+          <t>87,29; 97,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,34; 98,22</t>
+          <t>83,78; 97,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,59; 96,97</t>
+          <t>82,01; 96,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88,83; 98,15</t>
+          <t>88,55; 97,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85,85; 98,42</t>
+          <t>86,68; 98,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,19; 95,02</t>
+          <t>83,52; 94,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,33; 97,38</t>
+          <t>90,3; 96,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,56; 97,58</t>
+          <t>88,52; 97,51</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,51; 93,96</t>
+          <t>81,65; 93,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,51; 95,3</t>
+          <t>87,59; 95,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,45; 95,52</t>
+          <t>85,47; 95,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96,42; 99,56</t>
+          <t>96,04; 99,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,5; 96,87</t>
+          <t>91,33; 96,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,06; 89,72</t>
+          <t>79,02; 89,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,75; 97,13</t>
+          <t>92,89; 97,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,07; 95,46</t>
+          <t>91,09; 95,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82,95; 90,81</t>
+          <t>82,88; 90,74</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>82,02; 94,02</t>
+          <t>82,33; 93,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,53; 96,39</t>
+          <t>89,99; 96,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,66; 95,69</t>
+          <t>88,03; 95,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,61; 95,02</t>
+          <t>86,76; 95,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,79; 97,29</t>
+          <t>92,68; 97,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,84; 91,42</t>
+          <t>83,91; 91,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,77; 93,81</t>
+          <t>86,6; 93,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92,74; 96,56</t>
+          <t>92,61; 96,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>86,81; 92,18</t>
+          <t>87,23; 92,19</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>87,2; 92,21</t>
+          <t>86,69; 91,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>89,52; 93,02</t>
+          <t>89,42; 93,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,27; 93,29</t>
+          <t>89,32; 93,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89,69; 93,36</t>
+          <t>89,92; 93,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>90,06; 93,08</t>
+          <t>90,16; 93,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,53; 89,65</t>
+          <t>85,62; 89,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,37; 92,3</t>
+          <t>89,42; 92,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>90,37; 92,68</t>
+          <t>90,47; 92,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87,71; 90,44</t>
+          <t>87,64; 90,46</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54795; 62937</t>
+          <t>54414; 62915</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70107; 82458</t>
+          <t>69447; 82555</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56878; 68220</t>
+          <t>57302; 68992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91503; 102123</t>
+          <t>90878; 102093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110545; 128683</t>
+          <t>109597; 128793</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65854; 82517</t>
+          <t>65330; 82408</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>150568; 163111</t>
+          <t>150503; 163881</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>185559; 208568</t>
+          <t>186147; 208497</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>128323; 148291</t>
+          <t>127911; 148367</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59422; 67981</t>
+          <t>59369; 67995</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112174; 125257</t>
+          <t>114298; 125321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65066; 75743</t>
+          <t>64941; 75862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100794; 119576</t>
+          <t>100394; 119840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188936; 203155</t>
+          <t>188897; 203938</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114586; 127902</t>
+          <t>114968; 127960</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165098; 185759</t>
+          <t>165763; 185883</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>306907; 326312</t>
+          <t>308406; 326434</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>183341; 200985</t>
+          <t>185012; 201717</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55217; 65702</t>
+          <t>54950; 65848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81624; 91310</t>
+          <t>81155; 90690</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50203; 58125</t>
+          <t>50526; 58075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93244; 103179</t>
+          <t>92445; 103087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>115357; 130632</t>
+          <t>115873; 131525</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62954; 75254</t>
+          <t>62765; 75016</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>152524; 166826</t>
+          <t>151026; 166694</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>202829; 219793</t>
+          <t>201620; 220025</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117221; 131612</t>
+          <t>116673; 131196</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69156; 80797</t>
+          <t>69875; 80637</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87233; 103182</t>
+          <t>85811; 103438</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47558; 57178</t>
+          <t>48283; 57288</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96282; 110075</t>
+          <t>96696; 110399</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141885; 161052</t>
+          <t>141136; 161249</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99404; 112770</t>
+          <t>99833; 113164</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>171312; 188462</t>
+          <t>170561; 188276</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>234668; 260267</t>
+          <t>236416; 261471</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>151769; 167874</t>
+          <t>152060; 167198</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20494; 29301</t>
+          <t>19572; 29297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38036; 50685</t>
+          <t>39141; 50742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61514; 70881</t>
+          <t>60733; 71400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39841; 50683</t>
+          <t>40531; 50490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>73858; 86461</t>
+          <t>74165; 86438</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70644; 81155</t>
+          <t>70051; 81022</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64394; 77775</t>
+          <t>63859; 77771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>116627; 134619</t>
+          <t>117462; 135477</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>136405; 150435</t>
+          <t>136764; 150148</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45333; 57453</t>
+          <t>46534; 57554</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72049; 80228</t>
+          <t>71625; 80202</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52937; 61646</t>
+          <t>52587; 61447</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56510; 67161</t>
+          <t>56804; 66958</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>97846; 108111</t>
+          <t>97540; 107294</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60043; 68834</t>
+          <t>60621; 68891</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>108418; 122367</t>
+          <t>107560; 121854</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>173610; 187157</t>
+          <t>173551; 186408</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>117518; 129497</t>
+          <t>117475; 129395</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92050; 104819</t>
+          <t>91090; 104484</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>187917; 204642</t>
+          <t>188092; 204669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103422; 116978</t>
+          <t>104668; 117049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214480; 221471</t>
+          <t>213645; 221475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>259540; 274776</t>
+          <t>259052; 274516</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>161079; 182814</t>
+          <t>161002; 182271</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>309796; 324417</t>
+          <t>310260; 324936</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>453867; 475754</t>
+          <t>454004; 476611</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>270615; 296240</t>
+          <t>270378; 295999</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>110887; 127103</t>
+          <t>111305; 126554</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>188100; 202504</t>
+          <t>189063; 203223</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>200513; 216412</t>
+          <t>199078; 215568</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>170616; 187182</t>
+          <t>170904; 187273</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>331053; 347132</t>
+          <t>330691; 347075</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>269758; 294147</t>
+          <t>269987; 294259</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>288232; 311629</t>
+          <t>287672; 311367</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>525722; 547367</t>
+          <t>525014; 546790</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475622; 505046</t>
+          <t>477932; 505109</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>546033; 577409</t>
+          <t>542866; 575356</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>881615; 916099</t>
+          <t>880605; 917356</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>675488; 705880</t>
+          <t>675867; 707739</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>902148; 938991</t>
+          <t>904399; 938538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1366090; 1411974</t>
+          <t>1367614; 1410901</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>950221; 995994</t>
+          <t>951264; 995468</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1458464; 1506307</t>
+          <t>1459284; 1507798</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2260750; 2318630</t>
+          <t>2263198; 2319630</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1638097; 1689040</t>
+          <t>1636825; 1689541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,03; 97,16</t>
+          <t>84,76; 97,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,1; 92,85</t>
+          <t>79,31; 93,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,59; 93,42</t>
+          <t>76,96; 93,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,16; 97,92</t>
+          <t>88,33; 97,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,75; 91,36</t>
+          <t>78,31; 90,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,16; 83,46</t>
+          <t>66,69; 83,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,05; 96,96</t>
+          <t>88,93; 96,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,97; 90,7</t>
+          <t>81,28; 90,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,11; 85,96</t>
+          <t>73,85; 86,14</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,02; 98,51</t>
+          <t>85,5; 98,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,32; 96,84</t>
+          <t>88,43; 96,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,26; 94,92</t>
+          <t>81,49; 94,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,77; 86,87</t>
+          <t>73,12; 86,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,99; 96,08</t>
+          <t>89,05; 96,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,74; 95,43</t>
+          <t>85,21; 95,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,09; 89,81</t>
+          <t>79,95; 89,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,26; 95,54</t>
+          <t>89,95; 95,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,45; 94,26</t>
+          <t>86,73; 94,51</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,92; 94,57</t>
+          <t>79,27; 94,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,81; 97,01</t>
+          <t>86,5; 97,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,38; 96,99</t>
+          <t>84,18; 97,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,88; 98,0</t>
+          <t>88,51; 98,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,9; 94,09</t>
+          <t>83,02; 93,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,2; 93,47</t>
+          <t>77,46; 93,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,39; 95,35</t>
+          <t>86,53; 95,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,44; 94,33</t>
+          <t>86,82; 94,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,26; 93,62</t>
+          <t>83,53; 93,48</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,7; 94,28</t>
+          <t>81,3; 94,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,17; 93,02</t>
+          <t>79,14; 93,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,55; 96,75</t>
+          <t>81,65; 96,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,82; 94,56</t>
+          <t>82,86; 93,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,04; 89,16</t>
+          <t>78,06; 89,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,23; 95,48</t>
+          <t>84,23; 94,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,32; 93,08</t>
+          <t>84,23; 92,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,95; 89,53</t>
+          <t>80,78; 89,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,56; 94,08</t>
+          <t>86,0; 94,27</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63,16; 94,54</t>
+          <t>65,21; 94,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,25; 92,37</t>
+          <t>68,75; 92,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,85; 98,58</t>
+          <t>85,03; 97,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,54; 95,34</t>
+          <t>76,08; 94,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,23; 93,51</t>
+          <t>79,96; 93,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,45; 96,52</t>
+          <t>83,55; 96,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,07; 92,64</t>
+          <t>76,55; 92,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,7; 91,93</t>
+          <t>79,58; 91,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,46; 96,02</t>
+          <t>87,76; 96,09</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78,18; 96,69</t>
+          <t>77,42; 96,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,29; 97,75</t>
+          <t>87,37; 97,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,78; 97,9</t>
+          <t>84,1; 98,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,01; 96,67</t>
+          <t>81,48; 96,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88,55; 97,41</t>
+          <t>89,21; 98,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,68; 98,5</t>
+          <t>86,41; 98,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,52; 94,62</t>
+          <t>83,71; 94,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,3; 96,99</t>
+          <t>90,44; 97,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,52; 97,51</t>
+          <t>88,68; 97,63</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>81,65; 93,66</t>
+          <t>81,91; 93,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,59; 95,31</t>
+          <t>87,44; 95,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,47; 95,58</t>
+          <t>85,0; 95,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96,04; 99,56</t>
+          <t>96,35; 99,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,22 +1363,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,02; 89,46</t>
+          <t>79,58; 90,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,89; 97,28</t>
+          <t>92,94; 97,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,09; 95,63</t>
+          <t>91,31; 95,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82,88; 90,74</t>
+          <t>83,31; 91,14</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>82,33; 93,61</t>
+          <t>81,88; 93,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,99; 96,73</t>
+          <t>89,71; 96,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,03; 95,32</t>
+          <t>88,36; 95,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,76; 95,07</t>
+          <t>86,63; 95,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,68; 97,28</t>
+          <t>92,68; 97,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,91; 91,46</t>
+          <t>83,65; 91,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,6; 93,73</t>
+          <t>86,7; 93,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92,61; 96,46</t>
+          <t>92,95; 96,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>87,23; 92,19</t>
+          <t>86,93; 92,08</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,88</t>
+          <t>87,12; 92,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>89,42; 93,15</t>
+          <t>89,47; 93,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,32; 93,53</t>
+          <t>89,18; 93,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89,92; 93,31</t>
+          <t>89,79; 93,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>90,16; 93,01</t>
+          <t>90,09; 92,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,62; 89,6</t>
+          <t>85,51; 89,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,42; 92,39</t>
+          <t>89,36; 92,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>90,47; 92,72</t>
+          <t>90,32; 92,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87,64; 90,46</t>
+          <t>87,63; 90,59</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54414; 62915</t>
+          <t>54889; 62952</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69447; 82555</t>
+          <t>70516; 82709</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57302; 68992</t>
+          <t>56836; 69081</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90878; 102093</t>
+          <t>92090; 102133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109597; 128793</t>
+          <t>110389; 128079</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65330; 82408</t>
+          <t>65849; 82648</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>150503; 163881</t>
+          <t>150302; 163152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>186147; 208497</t>
+          <t>186849; 208851</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127911; 148367</t>
+          <t>127451; 148666</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59369; 67995</t>
+          <t>59012; 67996</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>114298; 125321</t>
+          <t>114436; 125152</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64941; 75862</t>
+          <t>65130; 75770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100394; 119840</t>
+          <t>100874; 119706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188897; 203938</t>
+          <t>189011; 203855</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114968; 127960</t>
+          <t>114256; 127994</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165763; 185883</t>
+          <t>165484; 184494</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>308406; 326434</t>
+          <t>307350; 326565</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>185012; 201717</t>
+          <t>185604; 202251</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54950; 65848</t>
+          <t>55196; 65733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81155; 90690</t>
+          <t>80857; 91308</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50526; 58075</t>
+          <t>50406; 58121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92445; 103087</t>
+          <t>93100; 103164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>115873; 131525</t>
+          <t>116046; 131242</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62765; 75016</t>
+          <t>62169; 74639</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>151026; 166694</t>
+          <t>151276; 166130</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>201620; 220025</t>
+          <t>202505; 220222</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116673; 131196</t>
+          <t>117054; 131000</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69875; 80637</t>
+          <t>69529; 80700</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85811; 103438</t>
+          <t>87998; 103852</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48283; 57288</t>
+          <t>48345; 57234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96696; 110399</t>
+          <t>96732; 109682</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141136; 161249</t>
+          <t>141177; 161315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99833; 113164</t>
+          <t>99830; 112528</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>170561; 188276</t>
+          <t>170385; 187733</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>236416; 261471</t>
+          <t>235921; 260924</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>152060; 167198</t>
+          <t>152849; 167546</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19572; 29297</t>
+          <t>20209; 29233</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39141; 50742</t>
+          <t>37769; 50813</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60733; 71400</t>
+          <t>61585; 70795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40531; 50490</t>
+          <t>40289; 49884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>74165; 86438</t>
+          <t>73909; 86486</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70051; 81022</t>
+          <t>70136; 81132</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63859; 77771</t>
+          <t>64262; 77359</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117462; 135477</t>
+          <t>117278; 134225</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>136764; 150148</t>
+          <t>137227; 150257</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46534; 57554</t>
+          <t>46086; 57447</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71625; 80202</t>
+          <t>71686; 80272</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52587; 61447</t>
+          <t>52783; 61670</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56804; 66958</t>
+          <t>56433; 66948</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>97540; 107294</t>
+          <t>98265; 108117</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60621; 68891</t>
+          <t>60437; 68804</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>107560; 121854</t>
+          <t>107809; 122102</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>173551; 186408</t>
+          <t>173830; 186569</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>117475; 129395</t>
+          <t>117686; 129558</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>91090; 104484</t>
+          <t>91376; 104586</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>188092; 204669</t>
+          <t>187770; 205065</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104668; 117049</t>
+          <t>104100; 117054</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213645; 221475</t>
+          <t>214328; 221467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>259052; 274516</t>
+          <t>259064; 274528</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>161002; 182271</t>
+          <t>162145; 183376</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>310260; 324936</t>
+          <t>310428; 325242</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>454004; 476611</t>
+          <t>455097; 476474</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>270378; 295999</t>
+          <t>271785; 297302</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>111305; 126554</t>
+          <t>110694; 126567</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>189063; 203223</t>
+          <t>188467; 202626</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>199078; 215568</t>
+          <t>199825; 216262</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>170904; 187273</t>
+          <t>170645; 187186</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>330691; 347075</t>
+          <t>330664; 347268</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>269987; 294259</t>
+          <t>269150; 293075</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>287672; 311367</t>
+          <t>287988; 310519</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>525014; 546790</t>
+          <t>526906; 547319</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>477932; 505109</t>
+          <t>476269; 504515</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>542866; 575356</t>
+          <t>545566; 576200</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>880605; 917356</t>
+          <t>881128; 917470</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>675867; 707739</t>
+          <t>674813; 705713</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>904399; 938538</t>
+          <t>903129; 938878</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1367614; 1410901</t>
+          <t>1366515; 1409518</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>951264; 995468</t>
+          <t>950051; 994923</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1459284; 1507798</t>
+          <t>1458314; 1506480</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2263198; 2319630</t>
+          <t>2259547; 2316987</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1636825; 1689541</t>
+          <t>1636538; 1691819</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
